--- a/backtest_runs/20260410_193731/by_symbol/FCCL/FCCL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FCCL/FCCL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3873.149999999995</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96126.85000000001</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>96126.85000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96126.85000000001</v>
@@ -771,7 +771,7 @@
         <v>-230.8499999999905</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>100769.5</v>
@@ -817,7 +817,7 @@
         <v>-4770.900000000017</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>95998.59999999999</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>95998.59999999999</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>95998.59999999999</v>
@@ -955,7 +955,7 @@
         <v>-1846.800000000015</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>94151.79999999997</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>101513.35</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>101513.35</v>
@@ -1185,7 +1185,7 @@
         <v>-3667.949999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>107592.4</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>107592.4</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>107592.4</v>
@@ -1415,7 +1415,7 @@
         <v>-3514.050000000012</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>117518.95</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>117518.95</v>
